--- a/excel_routes/route_JED_HBE_threats.xlsx
+++ b/excel_routes/route_JED_HBE_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F14F9CF8-3292-4F99-972D-FD14C27D3498}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E632A06A-C2A0-46D8-8E34-2AD3CE909270}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="44">
   <si>
     <t>Date</t>
   </si>
@@ -66,51 +66,63 @@
     <t>SM-454</t>
   </si>
   <si>
+    <t>EgyptAir MS-662</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>SAR</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-656</t>
+  </si>
+  <si>
+    <t>29-JUL-26</t>
+  </si>
+  <si>
+    <t>SM-452</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-173</t>
+  </si>
+  <si>
+    <t>30-JUL-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-171</t>
+  </si>
+  <si>
+    <t>01-AUG-26</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-175</t>
+  </si>
+  <si>
+    <t>MED</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-674</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
     <t>EgyptAir MS-644</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>SAR</t>
-  </si>
-  <si>
-    <t>29-JUL-26</t>
-  </si>
-  <si>
-    <t>SM-452</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-173</t>
-  </si>
-  <si>
-    <t>30-JUL-26</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-171</t>
-  </si>
-  <si>
-    <t>01-AUG-26</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-175</t>
-  </si>
-  <si>
-    <t>MED</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-666</t>
-  </si>
-  <si>
-    <t>EgyptAir MS-656</t>
-  </si>
-  <si>
     <t>SM-964</t>
   </si>
   <si>
     <t>02-AUG-26</t>
   </si>
   <si>
+    <t>Nile Air NP-128</t>
+  </si>
+  <si>
+    <t>EgyptAir MS-672</t>
+  </si>
+  <si>
     <t>03-AUG-26</t>
   </si>
   <si>
@@ -142,6 +154,9 @@
   </si>
   <si>
     <t>SM-458</t>
+  </si>
+  <si>
+    <t>flynas XY-565</t>
   </si>
 </sst>
 </file>
@@ -168,7 +183,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -191,6 +206,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF3CD"/>
         <bgColor rgb="FFFFF3CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8D7DA"/>
+        <bgColor rgb="FFF8D7DA"/>
       </patternFill>
     </fill>
   </fills>
@@ -221,7 +242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -233,6 +254,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -538,7 +562,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -625,31 +649,31 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="D3" s="2">
-        <v>399</v>
+        <v>651</v>
       </c>
       <c r="E3" s="2">
         <v>468</v>
       </c>
       <c r="F3" s="2">
-        <v>-69</v>
+        <v>183</v>
       </c>
       <c r="G3" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H3" s="2">
         <v>30</v>
       </c>
       <c r="I3" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>14</v>
@@ -660,13 +684,13 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="2">
         <v>399</v>
@@ -695,34 +719,34 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2">
-        <v>399</v>
+        <v>651</v>
       </c>
       <c r="E5" s="2">
-        <v>743</v>
+        <v>468</v>
       </c>
       <c r="F5" s="2">
-        <v>-344</v>
+        <v>183</v>
       </c>
       <c r="G5" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2">
         <v>30</v>
       </c>
       <c r="I5" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>23</v>
+        <v>-16</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>15</v>
@@ -730,34 +754,34 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D6" s="2">
-        <v>567</v>
+        <v>399</v>
       </c>
       <c r="E6" s="2">
-        <v>743</v>
+        <v>468</v>
       </c>
       <c r="F6" s="2">
-        <v>-176</v>
+        <v>-69</v>
       </c>
       <c r="G6" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2">
         <v>30</v>
       </c>
       <c r="I6" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>23</v>
+        <v>-10</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>15</v>
@@ -765,34 +789,34 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="2">
+        <v>399</v>
+      </c>
+      <c r="E7" s="2">
+        <v>810</v>
+      </c>
+      <c r="F7" s="2">
+        <v>-411</v>
+      </c>
+      <c r="G7" s="2">
+        <v>40</v>
+      </c>
+      <c r="H7" s="2">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="D7" s="2">
-        <v>567</v>
-      </c>
-      <c r="E7" s="2">
-        <v>743</v>
-      </c>
-      <c r="F7" s="2">
-        <v>-176</v>
-      </c>
-      <c r="G7" s="2">
-        <v>46</v>
-      </c>
-      <c r="H7" s="2">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -800,22 +824,22 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="2">
-        <v>919</v>
+        <v>427</v>
       </c>
       <c r="E8" s="2">
-        <v>743</v>
+        <v>810</v>
       </c>
       <c r="F8" s="2">
-        <v>176</v>
+        <v>-383</v>
       </c>
       <c r="G8" s="2">
         <v>46</v>
@@ -826,8 +850,8 @@
       <c r="I8" s="2">
         <v>-16</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>14</v>
+      <c r="J8" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -835,34 +859,34 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2">
-        <v>399</v>
+        <v>567</v>
       </c>
       <c r="E9" s="2">
-        <v>500</v>
+        <v>810</v>
       </c>
       <c r="F9" s="2">
-        <v>-101</v>
+        <v>-243</v>
       </c>
       <c r="G9" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2">
         <v>30</v>
       </c>
       <c r="I9" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -870,31 +894,31 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D10" s="2">
-        <v>399</v>
+        <v>919</v>
       </c>
       <c r="E10" s="2">
-        <v>531</v>
+        <v>810</v>
       </c>
       <c r="F10" s="2">
-        <v>-132</v>
+        <v>109</v>
       </c>
       <c r="G10" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2">
         <v>30</v>
       </c>
       <c r="I10" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>14</v>
@@ -905,31 +929,31 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="2">
-        <v>567</v>
+        <v>399</v>
       </c>
       <c r="E11" s="2">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="F11" s="2">
-        <v>36</v>
+        <v>-101</v>
       </c>
       <c r="G11" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2">
         <v>30</v>
       </c>
       <c r="I11" s="2">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>14</v>
@@ -940,31 +964,31 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="C12" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="E12" s="2">
         <v>500</v>
       </c>
       <c r="F12" s="2">
-        <v>-101</v>
+        <v>-73</v>
       </c>
       <c r="G12" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2">
         <v>30</v>
       </c>
       <c r="I12" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>14</v>
@@ -975,31 +999,31 @@
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D13" s="2">
-        <v>399</v>
+        <v>325</v>
       </c>
       <c r="E13" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F13" s="2">
-        <v>-101</v>
+        <v>-206</v>
       </c>
       <c r="G13" s="2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2">
         <v>30</v>
       </c>
       <c r="I13" s="2">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>14</v>
@@ -1010,22 +1034,22 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D14" s="2">
         <v>399</v>
       </c>
       <c r="E14" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F14" s="2">
-        <v>-101</v>
+        <v>-132</v>
       </c>
       <c r="G14" s="2">
         <v>40</v>
@@ -1045,22 +1069,22 @@
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D15" s="2">
-        <v>716</v>
+        <v>534</v>
       </c>
       <c r="E15" s="2">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="F15" s="2">
-        <v>216</v>
+        <v>3</v>
       </c>
       <c r="G15" s="2">
         <v>46</v>
@@ -1080,22 +1104,22 @@
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="2">
         <v>399</v>
       </c>
       <c r="E16" s="2">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="F16" s="2">
-        <v>-69</v>
+        <v>-101</v>
       </c>
       <c r="G16" s="2">
         <v>40</v>
@@ -1115,22 +1139,22 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D17" s="2">
         <v>399</v>
       </c>
       <c r="E17" s="2">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="F17" s="2">
-        <v>-69</v>
+        <v>-101</v>
       </c>
       <c r="G17" s="2">
         <v>40</v>
@@ -1150,22 +1174,22 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" s="2">
         <v>399</v>
       </c>
       <c r="E18" s="2">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="F18" s="2">
-        <v>-69</v>
+        <v>-101</v>
       </c>
       <c r="G18" s="2">
         <v>40</v>
@@ -1185,31 +1209,31 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D19" s="2">
-        <v>399</v>
+        <v>716</v>
       </c>
       <c r="E19" s="2">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="F19" s="2">
-        <v>-69</v>
+        <v>216</v>
       </c>
       <c r="G19" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2">
         <v>30</v>
       </c>
       <c r="I19" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>14</v>
@@ -1220,13 +1244,13 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D20" s="2">
         <v>399</v>
@@ -1255,13 +1279,13 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" s="2">
         <v>399</v>
@@ -1293,19 +1317,19 @@
         <v>32</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" s="2">
         <v>399</v>
       </c>
       <c r="E22" s="2">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="F22" s="2">
-        <v>-101</v>
+        <v>-69</v>
       </c>
       <c r="G22" s="2">
         <v>40</v>
@@ -1325,22 +1349,22 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D23" s="2">
         <v>399</v>
       </c>
       <c r="E23" s="2">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="F23" s="2">
-        <v>-101</v>
+        <v>-69</v>
       </c>
       <c r="G23" s="2">
         <v>40</v>
@@ -1360,22 +1384,22 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D24" s="2">
         <v>399</v>
       </c>
       <c r="E24" s="2">
-        <v>500</v>
+        <v>468</v>
       </c>
       <c r="F24" s="2">
-        <v>-101</v>
+        <v>-69</v>
       </c>
       <c r="G24" s="2">
         <v>40</v>
@@ -1395,31 +1419,31 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D25" s="2">
-        <v>399</v>
+        <v>427</v>
       </c>
       <c r="E25" s="2">
         <v>468</v>
       </c>
       <c r="F25" s="2">
-        <v>-69</v>
+        <v>-41</v>
       </c>
       <c r="G25" s="2">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2">
         <v>30</v>
       </c>
       <c r="I25" s="2">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>14</v>
@@ -1430,22 +1454,22 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D26" s="2">
         <v>399</v>
       </c>
       <c r="E26" s="2">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="F26" s="2">
-        <v>-69</v>
+        <v>-101</v>
       </c>
       <c r="G26" s="2">
         <v>40</v>
@@ -1465,22 +1489,22 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D27" s="2">
         <v>399</v>
       </c>
       <c r="E27" s="2">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="F27" s="2">
-        <v>-69</v>
+        <v>-101</v>
       </c>
       <c r="G27" s="2">
         <v>40</v>
@@ -1500,22 +1524,22 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D28" s="2">
         <v>399</v>
       </c>
       <c r="E28" s="2">
-        <v>531</v>
+        <v>500</v>
       </c>
       <c r="F28" s="2">
-        <v>-132</v>
+        <v>-101</v>
       </c>
       <c r="G28" s="2">
         <v>40</v>
@@ -1535,22 +1559,22 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D29" s="2">
         <v>399</v>
       </c>
       <c r="E29" s="2">
-        <v>531</v>
+        <v>468</v>
       </c>
       <c r="F29" s="2">
-        <v>-132</v>
+        <v>-69</v>
       </c>
       <c r="G29" s="2">
         <v>40</v>
@@ -1570,22 +1594,22 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D30" s="2">
         <v>399</v>
       </c>
       <c r="E30" s="2">
-        <v>531</v>
+        <v>468</v>
       </c>
       <c r="F30" s="2">
-        <v>-132</v>
+        <v>-69</v>
       </c>
       <c r="G30" s="2">
         <v>40</v>
@@ -1605,13 +1629,13 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D31" s="2">
         <v>399</v>
@@ -1640,22 +1664,22 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D32" s="2">
         <v>399</v>
       </c>
       <c r="E32" s="2">
-        <v>468</v>
+        <v>531</v>
       </c>
       <c r="F32" s="2">
-        <v>-69</v>
+        <v>-132</v>
       </c>
       <c r="G32" s="2">
         <v>40</v>
@@ -1675,22 +1699,22 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D33" s="2">
         <v>399</v>
       </c>
       <c r="E33" s="2">
-        <v>468</v>
+        <v>531</v>
       </c>
       <c r="F33" s="2">
-        <v>-69</v>
+        <v>-132</v>
       </c>
       <c r="G33" s="2">
         <v>40</v>
@@ -1710,36 +1734,246 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="2">
+        <v>399</v>
+      </c>
+      <c r="E34" s="2">
+        <v>531</v>
+      </c>
+      <c r="F34" s="2">
+        <v>-132</v>
+      </c>
+      <c r="G34" s="2">
+        <v>40</v>
+      </c>
+      <c r="H34" s="2">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D34" s="2">
-        <v>399</v>
-      </c>
-      <c r="E34" s="2">
+      <c r="B35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="2">
+        <v>399</v>
+      </c>
+      <c r="E35" s="2">
+        <v>468</v>
+      </c>
+      <c r="F35" s="2">
+        <v>-69</v>
+      </c>
+      <c r="G35" s="2">
+        <v>40</v>
+      </c>
+      <c r="H35" s="2">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="2">
+        <v>399</v>
+      </c>
+      <c r="E36" s="2">
+        <v>468</v>
+      </c>
+      <c r="F36" s="2">
+        <v>-69</v>
+      </c>
+      <c r="G36" s="2">
+        <v>40</v>
+      </c>
+      <c r="H36" s="2">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="2">
+        <v>399</v>
+      </c>
+      <c r="E37" s="2">
+        <v>468</v>
+      </c>
+      <c r="F37" s="2">
+        <v>-69</v>
+      </c>
+      <c r="G37" s="2">
+        <v>40</v>
+      </c>
+      <c r="H37" s="2">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38" s="2">
+        <v>399</v>
+      </c>
+      <c r="E38" s="2">
         <v>635</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F38" s="2">
         <v>-236</v>
       </c>
-      <c r="G34" s="2">
-        <v>40</v>
-      </c>
-      <c r="H34" s="2">
-        <v>30</v>
-      </c>
-      <c r="I34" s="2">
-        <v>-10</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K34" s="2" t="s">
+      <c r="G38" s="2">
+        <v>40</v>
+      </c>
+      <c r="H38" s="2">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="2">
+        <v>414</v>
+      </c>
+      <c r="E39" s="2">
+        <v>635</v>
+      </c>
+      <c r="F39" s="2">
+        <v>-221</v>
+      </c>
+      <c r="G39" s="2">
+        <v>30</v>
+      </c>
+      <c r="H39" s="2">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D40" s="2">
+        <v>534</v>
+      </c>
+      <c r="E40" s="2">
+        <v>635</v>
+      </c>
+      <c r="F40" s="2">
+        <v>-101</v>
+      </c>
+      <c r="G40" s="2">
+        <v>40</v>
+      </c>
+      <c r="H40" s="2">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2">
+        <v>-10</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K40" s="2" t="s">
         <v>15</v>
       </c>
     </row>
